--- a/data/trans_orig/P57B6_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023</t>
+          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>240553</t>
+          <t>242702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297104</t>
+          <t>299014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183130</t>
+          <t>177855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221718</t>
+          <t>221837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435929</t>
+          <t>437178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>504476</t>
+          <t>506098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245181</t>
+          <t>241546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>293595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283702</t>
+          <t>284261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323225</t>
+          <t>324803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540072</t>
+          <t>540540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>607218</t>
+          <t>608188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68095</t>
+          <t>68524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98812</t>
+          <t>99543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131582</t>
+          <t>131808</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163653</t>
+          <t>163928</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>208343</t>
+          <t>207964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>253428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44591</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>502619</t>
+          <t>503455</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>896120</t>
+          <t>932806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313516</t>
+          <t>314462</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>367976</t>
+          <t>364899</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>830400</t>
+          <t>830570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1363693</t>
+          <t>1320008</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>219731</t>
+          <t>196867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>526097</t>
+          <t>525487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>366521</t>
+          <t>370271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>418438</t>
+          <t>421576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>544327</t>
+          <t>576363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>922804</t>
+          <t>928145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57156</t>
+          <t>55084</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143804</t>
+          <t>146358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174545</t>
+          <t>173197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215922</t>
+          <t>216102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>201177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356289</t>
+          <t>350594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34713</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>29008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283761</t>
+          <t>284739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345168</t>
+          <t>345172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121105</t>
+          <t>112598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309452</t>
+          <t>307648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330924</t>
+          <t>327071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>637440</t>
+          <t>639084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>259261</t>
+          <t>256214</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315466</t>
+          <t>315790</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>435495</t>
+          <t>436388</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>737677</t>
+          <t>751141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>711522</t>
+          <t>711410</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1155093</t>
+          <t>1160265</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63435</t>
+          <t>64921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102322</t>
+          <t>103305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56129</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152238</t>
+          <t>153221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123352</t>
+          <t>122011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>234538</t>
+          <t>235785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45050</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30124</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>62863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>330213</t>
+          <t>326735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>396259</t>
+          <t>394410</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245904</t>
+          <t>246891</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>341178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>591020</t>
+          <t>578630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>721157</t>
+          <t>715813</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348313</t>
+          <t>347744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>414035</t>
+          <t>417665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>449101</t>
+          <t>450761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>623348</t>
+          <t>623562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>823642</t>
+          <t>825194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1025643</t>
+          <t>1020532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>138145</t>
+          <t>135502</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>185347</t>
+          <t>185206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>194978</t>
+          <t>193484</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>278933</t>
+          <t>279828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>354946</t>
+          <t>356532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>448961</t>
+          <t>442343</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>50570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75642</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1441229</t>
+          <t>1438132</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2037692</t>
+          <t>2033608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>863945</t>
+          <t>870466</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1166183</t>
+          <t>1178093</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2437103</t>
+          <t>2426709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3169589</t>
+          <t>3146648</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1015563</t>
+          <t>1025184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1465567</t>
+          <t>1466512</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1611689</t>
+          <t>1598905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2115945</t>
+          <t>2131137</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3099078</t>
+          <t>3099079</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2798712</t>
+          <t>2799199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3414110</t>
+          <t>3491270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>335889</t>
+          <t>330959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>484064</t>
+          <t>488097</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>574740</t>
+          <t>569020</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>766299</t>
+          <t>770538</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>998685</t>
+          <t>984445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1232608</t>
+          <t>1235354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52758</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>93915</t>
+          <t>92291</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>133728</t>
+          <t>133989</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>157139</t>
+          <t>153923</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>216010</t>
+          <t>214137</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">

--- a/data/trans_orig/P57B6_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>268172</t>
+          <t>291768</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242702</t>
+          <t>263882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299014</t>
+          <t>323672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>200724</t>
+          <t>219698</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177855</t>
+          <t>196258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221837</t>
+          <t>241989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>468895</t>
+          <t>511467</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>437178</t>
+          <t>477264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>506098</t>
+          <t>549991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>269137</t>
+          <t>293165</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241546</t>
+          <t>264868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293595</t>
+          <t>318954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>303756</t>
+          <t>328621</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284261</t>
+          <t>306225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324803</t>
+          <t>349754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>572894</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540540</t>
+          <t>586945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>608188</t>
+          <t>656372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>88312</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>105626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147957</t>
+          <t>159959</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131808</t>
+          <t>141621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163928</t>
+          <t>178732</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>230612</t>
+          <t>248271</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>207964</t>
+          <t>221886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253428</t>
+          <t>272523</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>20395</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>28697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43985</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634048</t>
+          <t>689224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634048</t>
+          <t>689224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634048</t>
+          <t>689224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>671430</t>
+          <t>728673</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671430</t>
+          <t>728673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>671430</t>
+          <t>728673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1305478</t>
+          <t>1417897</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1305478</t>
+          <t>1417897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1305478</t>
+          <t>1417897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>656201</t>
+          <t>451940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503455</t>
+          <t>418329</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>932806</t>
+          <t>491430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>339658</t>
+          <t>374883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>314462</t>
+          <t>347949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>364899</t>
+          <t>404811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>995860</t>
+          <t>826823</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>830570</t>
+          <t>782655</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1320008</t>
+          <t>878109</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>407374</t>
+          <t>453966</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196867</t>
+          <t>415201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>525487</t>
+          <t>489551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>394523</t>
+          <t>448191</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>370271</t>
+          <t>419842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>421576</t>
+          <t>476495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>801898</t>
+          <t>902157</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>576363</t>
+          <t>856861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>928145</t>
+          <t>947791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>107922</t>
+          <t>120703</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>99657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146358</t>
+          <t>143353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>194762</t>
+          <t>215694</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173197</t>
+          <t>193781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216102</t>
+          <t>238124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>302684</t>
+          <t>336397</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201177</t>
+          <t>309451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350594</t>
+          <t>369298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -1633,102 +1633,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>35197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27707</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19783</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38190</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>49127</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>36295</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>65706</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25135</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17880</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>34989</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>45692</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>29008</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>62753</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192054</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192054</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192054</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>954079</t>
+          <t>1066474</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>954079</t>
+          <t>1066474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>954079</t>
+          <t>1066474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2146134</t>
+          <t>2114503</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2146134</t>
+          <t>2114503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2146134</t>
+          <t>2114503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>314410</t>
+          <t>353190</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284739</t>
+          <t>322406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345172</t>
+          <t>390051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>230509</t>
+          <t>268691</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>243255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>307648</t>
+          <t>292653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>544919</t>
+          <t>621880</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327071</t>
+          <t>576167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>639084</t>
+          <t>659763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>286069</t>
+          <t>334184</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>256214</t>
+          <t>302305</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315790</t>
+          <t>362326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>556463</t>
+          <t>373910</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>436388</t>
+          <t>349086</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>751141</t>
+          <t>402658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>842532</t>
+          <t>708094</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>711410</t>
+          <t>670956</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1160265</t>
+          <t>752096</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>82152</t>
+          <t>93230</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>75415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103305</t>
+          <t>117276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>113006</t>
+          <t>133311</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55791</t>
+          <t>115880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>156319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>195157</t>
+          <t>226541</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122011</t>
+          <t>200394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>235785</t>
+          <t>258609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44469</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47682</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62863</t>
+          <t>65847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>699861</t>
+          <t>798752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>699861</t>
+          <t>798752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>699861</t>
+          <t>798752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>930429</t>
+          <t>809056</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>930429</t>
+          <t>809056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>930429</t>
+          <t>809056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1630290</t>
+          <t>1607808</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1630290</t>
+          <t>1607808</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1630290</t>
+          <t>1607808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>361534</t>
+          <t>388271</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>326735</t>
+          <t>356974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>394410</t>
+          <t>423462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>306581</t>
+          <t>336248</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>246891</t>
+          <t>308664</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341178</t>
+          <t>364350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>668115</t>
+          <t>724519</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>578630</t>
+          <t>683599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>715813</t>
+          <t>769735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>381972</t>
+          <t>403472</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>347744</t>
+          <t>370578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>417665</t>
+          <t>435327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>499784</t>
+          <t>465856</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>450761</t>
+          <t>439343</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>623562</t>
+          <t>494340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>881755</t>
+          <t>869328</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>825194</t>
+          <t>825340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1020532</t>
+          <t>912524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>159494</t>
+          <t>173192</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135502</t>
+          <t>148927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>185206</t>
+          <t>197416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>248916</t>
+          <t>270792</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>193484</t>
+          <t>244741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279828</t>
+          <t>296925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>408411</t>
+          <t>443984</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>356532</t>
+          <t>408310</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>442343</t>
+          <t>478902</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -2771,22 +2771,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>33754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>46145</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50570</t>
+          <t>58230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60121</t>
+          <t>68149</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>84895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>923470</t>
+          <t>986939</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>923470</t>
+          <t>986939</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>923470</t>
+          <t>986939</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2018402</t>
+          <t>2105980</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2018402</t>
+          <t>2105980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2018402</t>
+          <t>2105980</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1600317</t>
+          <t>1485169</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1438132</t>
+          <t>1422560</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2033608</t>
+          <t>1554014</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1077472</t>
+          <t>1199519</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>870466</t>
+          <t>1147101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1178093</t>
+          <t>1251858</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2677789</t>
+          <t>2684688</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2426709</t>
+          <t>2595396</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3146648</t>
+          <t>2768743</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1344552</t>
+          <t>1484787</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1025184</t>
+          <t>1425522</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1466512</t>
+          <t>1553364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1754527</t>
+          <t>1616578</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1598905</t>
+          <t>1563148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2131137</t>
+          <t>1668082</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3099079</t>
+          <t>3101365</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2799199</t>
+          <t>3016646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3491270</t>
+          <t>3191830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>432223</t>
+          <t>475437</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>330959</t>
+          <t>433688</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>488097</t>
+          <t>518150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>704641</t>
+          <t>779756</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>569020</t>
+          <t>740827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>770538</t>
+          <t>823591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1136864</t>
+          <t>1255193</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>984445</t>
+          <t>1195819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1235354</t>
+          <t>1318389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53257</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>92291</t>
+          <t>98600</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>94329</t>
+          <t>110881</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>133989</t>
+          <t>150211</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>186572</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>153923</t>
+          <t>178611</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>214137</t>
+          <t>235062</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
